--- a/notebooks/추출 골든셋 단위 분리.xlsx
+++ b/notebooks/추출 골든셋 단위 분리.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="추출_골든셋_단위분리" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,1516 +480,1152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A021-01</t>
+          <t>A001-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A021</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>수출·무역</t>
+          <t>인구</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6월 1~20일 수출 8.3% 증가... 반도체 21.8%↑ 車 9.2%↑</t>
+          <t>2024년 서울 인구 5년 만에 최저치 기록</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>관세청에 따르면 지난 1~20일 수출액은 386억7200만달러로 전년 동기 대비 8.3% 증가했다.</t>
+          <t>서울 인구가 2024년 기준 5년 만에 최저치를 기록했다</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.300000000000001</v>
+        <v>9384000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2025-06-01~06-20</t>
-        </is>
+          <t>명</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2024</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2024년 동기 대비</t>
+          <t>2019년 대비</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
+          <t>claim_extractor.py + 사람 교정</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/23/VRSULF3KLRDCXJYUXRMNW45AIY</t>
+          <t>https://www.chosun.com/economy/market_trend/2025/05/05/CUZARKRUGNBKBAQJ6TAN3QAHG4/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A021-02</t>
+          <t>A001-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A021</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>수출·무역</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6월 1~20일 수출 8.3% 증가... 반도체 21.8%↑ 車 9.2%↑</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>반도체와 승용차 등 주력 수출 품목이 각각 21.8%, 9.2% 늘어난 영향이 컸다.</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2025-06-01~06-20</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2024년 동기 대비</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>배스킨라빈스 스푼이 놀이터로... 어린이대공원에 '핑크드림가든' 오픈</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/23/VRSULF3KLRDCXJYUXRMNW45AIY</t>
+          <t>https://www.chosun.com/economy/market_trend/2025/05/05/CUZARKRUGNBKBAQJ6TAN3QAHG4/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A021-03</t>
+          <t>A002-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A021</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>수출·무역</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6월 1~20일 수출 8.3% 증가... 반도체 21.8%↑ 車 9.2%↑</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>반도체와 승용차 등 주력 수출 품목이 각각 21.8%, 9.2% 늘어난 영향이 컸다.</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2025-06-01~06-20</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2024년 동기 대비</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>"매우 훌륭하다"… 트럼프 손녀 카이 트럼프도 엄지 척한 K푸드</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/23/VRSULF3KLRDCXJYUXRMNW45AIY</t>
+          <t>https://www.chosun.com/economy/market_trend/2025/05/05/IPC4VQYJIZEWJB7AGYF5HVYPMU</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A022-01</t>
+          <t>A003-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A022</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>소매판매</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>금리 0.25%p 내린 한은... 관세 폭탄·내수 부진에 경기 살리기 선택</t>
+          <t>백종원, '방송활동 중단' 승부수… 오버행 부담 덜까</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>통계청 발표에 따르면 작년 전국 17개 모든 시도에서 소매 판매가 감소한 것으로 나타났다. 전국적으로는 2.2% 감소했고</t>
+          <t>상장 첫날 더본코리아 주식은 공모가(3만4000원)보다 51.18%(1만7400원) 오른 5만1400원에 거래를 마쳤다.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>51400</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2024년(연간)</t>
-        </is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2025.05</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2023년 대비</t>
+          <t>공모가(3만4000원)보다</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
+          <t>claim_extractor.py + 사람 교정</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/25/2RBIFVNKT5ELXID4FUQCFM63G4</t>
+          <t>https://www.chosun.com/economy/money/2025/05/06/3BM2ISQL2LODMSN4VOI4WGL5QY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A022-02</t>
+          <t>A003-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A022</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>고용(건설업)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>금리 0.25%p 내린 한은... 관세 폭탄·내수 부진에 경기 살리기 선택</t>
+          <t>백종원, '방송활동 중단' 승부수… 오버행 부담 덜까</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>지난달 건설업 취업자 수는 192만 1000명으로, 코로나 팬데믹 시기였던 2021년 이후 처음으로 200만명 아래로 내려갔다</t>
+          <t>더본코리아 주가는 지난 2일 종가 2만6950원으로 공모가보다 20% 낮은 수준에 머물렀다.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1921000</v>
+        <v>26950</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2025년 1월</t>
-        </is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2025.05</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2021년 이후 최초(200만명 하회)</t>
+          <t>공모가(3만4000원)보다</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
+          <t>claim_extractor.py + 사람 교정</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/25/2RBIFVNKT5ELXID4FUQCFM63G4</t>
+          <t>https://www.chosun.com/economy/money/2025/05/06/3BM2ISQL2LODMSN4VOI4WGL5QY</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A022-03</t>
+          <t>A004-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A022</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>수출·무역</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>금리 0.25%p 내린 한은... 관세 폭탄·내수 부진에 경기 살리기 선택</t>
+          <t>육아휴직 핀란드 국방장관, 출산휴가 英 검찰총장… 저출생 해법 들려줘</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 관세청에 따르면 이달 1~20일 수출액은 353억달러로 전년보다 16% 늘었지만,</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>16</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2025-02-01~02-20</t>
-        </is>
+          <t>지난 5일 어린이날에는 지난달 말 기준 국내 어린이(0~14세) 수가 역대 최저치를 기록했다는 소식이 전해졌다.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>역대 최저치</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>2025.05</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2024년 동기 대비</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>지난달 말 기준(25.04)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/25/2RBIFVNKT5ELXID4FUQCFM63G4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/07/MXYHVYYN4FBV3ONTCKIGEJ74U4/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A023-01</t>
+          <t>A005-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A023</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소비자물가</t>
+          <t>산업</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>물가상승률 석 달째 2%대...업체들 줄인상에 가공식품·외식 가격 ↑</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2일 통계청이 발표한 ‘3월 소비자물가 동향’에 따르면, 지난달 소비자물가 지수는 116.29로 전년 동월 대비 2.1% 상승했다.</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2025년 3월</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2024년 3월 대비</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>롯데월드 피카츄 퍼레이드</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/04/02/EZEOHOZC5NBBHKNEXYWAAYWO24</t>
+          <t>https://www.chosun.com/economy/industry-company/2025/05/07/4NB5Y3KUQRD2NIXMLXXLF5XJZQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A023-02</t>
+          <t>A006-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A023</t>
+          <t>A006</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>소비자물가(가공식품)</t>
+          <t>산업</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>물가상승률 석 달째 2%대...업체들 줄인상에 가공식품·외식 가격 ↑</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>지난달 가공식품 물가는 전년 동월 대비 3.6% 올랐는데, 지난해 1월(3.2%) 이후 14개월 만에 최대 증가폭이다.</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2025년 3월</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2024년 3월 대비</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>최태원 회장 "SKT 해킹으로 불편 겪은 모든 분께 사과… 일련의 대응 미흡"</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/04/02/EZEOHOZC5NBBHKNEXYWAAYWO24</t>
+          <t>https://www.chosun.com/economy/industry-company/2025/05/07/DYC2374NXFC7VE53X5DW6C5B7U/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A023-03</t>
+          <t>A007-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A023</t>
+          <t>A007</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>소비자물가(외식)</t>
+          <t>사회</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>물가상승률 석 달째 2%대...업체들 줄인상에 가공식품·외식 가격 ↑</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>외식 물가는 지난 2월(3%)에 이어 지난달에도 3% 상승했는데,</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2025년 3월</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2024년 3월 대비</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>귀가 중 여성 강제추행 40대 2심서 무죄로 뒤집힌 이유는</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/04/02/EZEOHOZC5NBBHKNEXYWAAYWO24</t>
+          <t>https://www.chosun.com/national/regional/2025/05/08/OE43CJZUY5D4TLLNYTZEUDWD4I</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A024-01</t>
+          <t>A008-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A024</t>
+          <t>A008</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>인구동향(출생)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>작년 11월 출생아 14.6% 증가...2010년 이후 최대폭</t>
+          <t>"3단계 스트레스 DSR, 수도권·지방 차등"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">22일 통계청이 22일 발표한 ‘2024년 11월 인구동향’에 따르면, 작년 11월 출생아 수는 1년 전에 비해 14.6% 늘어난 2만95명으로 집계됐다. </t>
+          <t>금융 당국은 작년 2월 은행권 주택담보대출에 0.38%의 스트레스 DSR 금리를 붙이는 1단계 조치를 도입했고, 9월부터는 2단계로 은행권 주택담보대출·신용대출과 2금융권 주택담보대출에 수도권 1.2%, 비수도권 0.75%의 스트레스 금리를 적용해왔다.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>20095</v>
+        <v>0.38</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2024년 11월</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2025.05</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2023년 11월 대비</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>작년 2월(24.02)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/22/HAHTAVPQ75BJXM4GWC4SNRKAZA</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/08/73WTZHCJQJBNFCCUPRE3O7H344</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A024-02</t>
+          <t>A009-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A024</t>
+          <t>A009</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>인구동향(누계 출생)</t>
+          <t>자동차</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>작년 11월 출생아 14.6% 증가...2010년 이후 최대폭</t>
+          <t>美 자동차 '빅3', 관세 역풍에 동반 부진</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>작년 1월부터 11월까지 출생아 수 22만94명으로 전년에 비해 3% 늘어났다.</t>
+          <t>미국이 모든 수입차에 부과하는 25% 관세가 2분기부터 본격 영향을 미치면서, 연간 실적 전망치를 대폭 낮춰 잡거나 전망 자체를 포기하는 사례가 잇따르고 있다.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>220094</v>
+        <v>0.25</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2024년 1~11월 누계</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2023년 1~11월 대비</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>2025.05</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/22/HAHTAVPQ75BJXM4GWC4SNRKAZA</t>
+          <t>https://www.chosun.com/economy/auto/2025/05/08/4CDVS52635DE3NN6AUYLF6VRB4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A024-03</t>
+          <t>A010-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A024</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>인구동향(혼인)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>작년 11월 출생아 14.6% 증가...2010년 이후 최대폭</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>향후 혼인 추이가 현재의 출생 증가세 유지를 결정하는 주요 변수로 지목되는 가운데, 작년 11월 혼인 건수는 1만8581건으로 1년 전 대비 11.3% 늘었다.</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>18581</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>건</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2024년 11월</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2023년 11월 대비</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>김범석 직무대행 두 번째 F4 회의..."금융·외환시장 24시간 모니터링 지속"</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/22/HAHTAVPQ75BJXM4GWC4SNRKAZA</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/08/DNRWHXVTDZBIJK362H2STC7QOE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A025-01</t>
+          <t>A011-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A025</t>
+          <t>A011</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>인구동향(연간 혼인)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>작년 혼인 건수 15% 늘어...증가율 1970년 집계 이래 최고</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">통계청이 26일 발표한 ‘2024년 12월 인구동향’에 따르면, 작년 한해 혼인 건수는 22만2422건으로 전년 대비 14.9% 늘었다. </t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>222422</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>건</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2024년(연간)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2023년 대비</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>"직무에 충실한 공직자 외부서 흔들어선 안돼"</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/26/GSSMZGGYMBGKXLHSR4WOOWUCQ4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/08/GMETCI2MP5APBOKG7X7NW6DXZU</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A025-02</t>
+          <t>A012-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A025</t>
+          <t>A012</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인구동향(12월 혼인)</t>
+          <t>겅제</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>작년 혼인 건수 15% 늘어...증가율 1970년 집계 이래 최고</t>
+          <t>中 "시행착오 허용"… '용착' 개념 제도화, 실패 무릅쓰고 연구</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>작년 12월 혼인 건수는 2만2519건에 달해 전년 동월 대비 28.1% 늘었다.</t>
+          <t xml:space="preserve">한국산업기술기획평가원에 따르면, 2017~2022년 우리나라의 국가 주도 R&amp;D 과제 성공률은 97% 밑으로 내려간 적이 한 번도 없다. </t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>22519</v>
+        <v>0.97</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>건</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2024년 12월</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2025.05</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2023년 12월 대비</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>2017~2022년</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/26/GSSMZGGYMBGKXLHSR4WOOWUCQ4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/08/OBWUVLVHBBASRFQEDJGCJ4NP2Y</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A025-03</t>
+          <t>A013-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A025</t>
+          <t>A013</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>인구동향(이혼)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>작년 혼인 건수 15% 늘어...증가율 1970년 집계 이래 최고</t>
+          <t>한국이 R&amp;D 나눠먹을 때… 중국은 '떡잎' 골라 몰아줬다</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">작년 이혼 건수는 9만1155건으로 전년(9만1155건) 대비 1.3% 줄었다. </t>
+          <t>AI 관련 R&amp;D 예산은 1조2000억원으로 정부 R&amp;D의 약 4% 수준이다.</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>91155</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>건</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2024년(연간)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2023년 대비 (※원문 전년치 표기 오타 확인 필요)</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>조원</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2025.05</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/26/GSSMZGGYMBGKXLHSR4WOOWUCQ4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/08/P5U6GYQISBFYVG6Q4NRZDH3YFE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A026-01</t>
+          <t>A013-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A026</t>
+          <t>A013</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>가계동향(전체 소득)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1분기 가구당 月 소득 1년 새 4.5% 늘었지만 저소득층은 1.5% 줄어</t>
+          <t>한국이 R&amp;D 나눠먹을 때… 중국은 '떡잎' 골라 몰아줬다</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29일 통계청은 ’2025년 1분기 가계동향 조사 결과’에서, 올해 1분기 가구당 월평균 소득이 535만1000원으로 지난해 같은 기간 대비 4.5% 증가했다고 밝혔다.</t>
+          <t>AI 관련 R&amp;D 예산은 1조2000억원으로 정부 R&amp;D의 약 4% 수준이다.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5351000</v>
+        <v>4</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>원</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2025년 1분기</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2024년 1분기 대비</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2025.05</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/05/30/PVQ5FXMBSFCETC4MIINOSK535M</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/08/P5U6GYQISBFYVG6Q4NRZDH3YFE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A026-02</t>
+          <t>A014-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A026</t>
+          <t>A014</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>가계동향(저소득층 소득)</t>
+          <t>산업</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1분기 가구당 月 소득 1년 새 4.5% 늘었지만 저소득층은 1.5% 줄어</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>소득 하위 20%(1분위) 가구의 월평균 소득은 114만원으로 1년 전보다 1.5% 줄었다.</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1140000</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>원</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2025년 1분기</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2024년 1분기 대비</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>이재명, 경제5단체 간담회..."민생, 경제 살리기의 중심은 기업"</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/05/30/PVQ5FXMBSFCETC4MIINOSK535M</t>
+          <t>https://www.chosun.com/economy/industry-company/2025/05/08/4IBLYDSMDNEZDILCVFNENFA5KE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A026-03</t>
+          <t>A015-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A026</t>
+          <t>A015</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>가계동향(소득분배지표)</t>
+          <t>자동차</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1분기 가구당 月 소득 1년 새 4.5% 늘었지만 저소득층은 1.5% 줄어</t>
+          <t>영국車 관세 10%로 인하... 美 빅3 "우리 차 산업에 해 끼칠 것" 반발</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 이에 가구원 수가 같다고 가정해 상위 20%의 소득이 하위 20%의 몇 배인지를 보여주는 지표인 균등화 처분가능소득 5분위 배율은 1분기 6.32배로 전년 같은 기간의 5.98배보다 올랐다. </t>
+          <t>미국이 영국산 자동차에 대한 품목별 관세를 연간 10만대에 한해 기존 27.5%에서 10%로 낮추기로 하자 특혜라며 반발하는 것이다.</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6.32</v>
+        <v>0.1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>배</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2025년 1분기</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2025.05</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2024년 1분기(5.98배) 대비</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>기존 27.5%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/05/30/PVQ5FXMBSFCETC4MIINOSK535M</t>
+          <t>https://www.chosun.com/economy/auto/2025/05/09/TDXX7IAYGFD77DFG3LJTUMJHQA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A027-01</t>
+          <t>A015-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A027</t>
+          <t>A015</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>소비자물가(전체)</t>
+          <t>자동차</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>돼지고기·계란 고공행진… 축산물 물가 6% 올라</t>
+          <t>영국車 관세 10%로 인하... 美 빅3 "우리 차 산업에 해 끼칠 것" 반발</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4일 통계청은 ‘5월 소비자 물가 동향’에서 지난달 소비자 물가가 전년 동월 대비 1.9% 올랐다고 밝혔다.</t>
+          <t>컨설팅업체 글로벌데이터에 따르면 지난해 빅3가 미국으로 수입한 차량은 221만대로, 미국 전체 자동차 수입량(802만대)의 28%에 이른다.</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.9</v>
+        <v>221</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2025년 5월</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2024년 5월 대비</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>만대</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2025.05</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/05/7CAZV7VZIVDGVJTCK22YR6RKMI</t>
+          <t>https://www.chosun.com/economy/auto/2025/05/09/TDXX7IAYGFD77DFG3LJTUMJHQA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A027-02</t>
+          <t>A015-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A027</t>
+          <t>A015</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>소비자물가(축산물)</t>
+          <t>자동차</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>돼지고기·계란 고공행진… 축산물 물가 6% 올라</t>
+          <t>영국車 관세 10%로 인하... 美 빅3 "우리 차 산업에 해 끼칠 것" 반발</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>하지만 지난달 돼지고기(8.4%), 국산 쇠고기(5.3%), 계란(3.8%) 등의 가격이 일제히 오르며, 축산물 가격 상승 폭은 6.2%를 기록했다.</t>
+          <t>영국의 대미 자동차 수출은 64억파운드(약 12조원)로 대미 수출 품목 1위다.</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6.2</v>
+        <v>64</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2025년 5월</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2024년 5월 대비</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>억 파운드</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2025.05</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/05/7CAZV7VZIVDGVJTCK22YR6RKMI</t>
+          <t>https://www.chosun.com/economy/auto/2025/05/09/TDXX7IAYGFD77DFG3LJTUMJHQA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A027-03</t>
+          <t>A016-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A027</t>
+          <t>A016</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>소비자물가(생활물가)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>돼지고기·계란 고공행진… 축산물 물가 6% 올라</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>이에 가격이 변하면 소비자들이 민감하게 반응하는 144품목만 추려서 작성한 생활 물가는 전년 동월 대비 2.3% 오르며, 올 들어 최저 상승 폭을 보였다.</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2025년 5월</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2024년 5월 대비</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>13일까지 전통시장 84곳서 수산물 온누리상품권 환급</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/05/7CAZV7VZIVDGVJTCK22YR6RKMI</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/09/KA2MHX4JQVDUVGXRIRGOTNKYQA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A028-01</t>
+          <t>A017-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A028</t>
+          <t>A017</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>사회조사(삶의 만족도)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>한국 국민 삶 만족도 OECD 38국 중 33위</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>24일 통계청은 ‘국민 삶의 질 2024’ 보고서에서 우리나라 국민들의 지난 3년간(2021~2023년) 평균 삶의 만족도 점수가 6.06점을 기록했다고 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>점</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">	2021~2023년 평균</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>OECD 38개국 순위 비교(33위)</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>KDI "구조 개혁 안 하면 2041년부터 마이너스 성장"</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/25/7PFLVADLU5CBDNFI3Q4SI5DAEU</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/09/P47TDIUWFNGBTDVIS6AWFNINNU</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A028-02</t>
+          <t>A018-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A028</t>
+          <t>A018</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>사회조사(삶의 만족도)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>한국 국민 삶 만족도 OECD 38국 중 33위</t>
+          <t>한때 '미운 오리' 방산… 반도체·바이오에 이어 3대 산업으로 급성장</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2023년 우리나라 국민들의 삶의 만족도는 10점 만점에 6.4점으로 전년 대비 0.1점 감소했다.</t>
+          <t xml:space="preserve">일 한국거래소에 따르면 방산·조선주 시가총액 상위 10종목의 시장가치 합계는 전날 기준 129조원을 기록했다. </t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6.4</v>
+        <v>129</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>점</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2023년</t>
-        </is>
+          <t>조원</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>2025.05</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2022년 대비</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>전날 기준(25.05.08)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/25/7PFLVADLU5CBDNFI3Q4SI5DAEU</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/09/SGOIEYQ3P5BA3AGPPOVMZHPREQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A029-01</t>
+          <t>A018-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A029</t>
+          <t>A018</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>교육(고학력자 비율)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>女 대졸 이상 비율, 80년대생부터 男 앞서</t>
+          <t>한때 '미운 오리' 방산… 반도체·바이오에 이어 3대 산업으로 급성장</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>반면 1980~1984년생부터는 여성의 고학력자 비율이 72.1%로 남성(69.4%)을 2.7%포인트 앞섰다.</t>
+          <t>같은 날 자동차 업종 상위 10종목 시가총액 합계는 109조원에 그쳤다.</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>72.09999999999999</v>
+        <v>109</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>1980~1984년생 코호트</t>
-        </is>
+          <t>조원</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2025.05</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>남성(69.4%) 대비</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>전날 기준(25.05.09)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/28/FV56ZTW6QJB45D7N322ZPHFHYU</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/09/SGOIEYQ3P5BA4AGPPOVMZHPREQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A029-02</t>
+          <t>A018-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A029</t>
+          <t>A018</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>교육(고학력자 비율)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>女 대졸 이상 비율, 80년대생부터 男 앞서</t>
+          <t>한때 '미운 오리' 방산… 반도체·바이오에 이어 3대 산업으로 급성장</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1990~1994년생 여성의 대학 이상 졸업자 비율은 78.5%로 남성(65.3%)보다 무려 13%포인트 이상 높았다.</t>
+          <t xml:space="preserve"> 작년 말에는 상황이 달랐다. 방산·조선 대표 기업들의 시가총액은 67조원으로 자동차 기업군(129조원)의 52% 수준에 불과했다.</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>78.5</v>
+        <v>67</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1990~1994년생 코호트</t>
-        </is>
+          <t>조원</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2025.05</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>남성(65.3%) 대비</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>작년 말</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/28/FV56ZTW6QJB45D7N322ZPHFHYU</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/09/SGOIEYQ3P5BA5AGPPOVMZHPREQ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A030-01</t>
+          <t>A019-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A030</t>
+          <t>A019</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>경제성장 (⚠판단불가 후보)</t>
+          <t>경제</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>정부 "올해 경제성장률 1.8%"… 한은 전망보다 더 낮췄다</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>수출과 건설 경기 부진 여파로 새해 우리나라 경제가 1.8% 성장하는 데 그칠 것이라고 기획재정부가 2일 전망했다.</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2025년(전망치)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>한국은행 전망(1.9%) 대비</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>롯데손보, 900억대 후순위채 조기 상환 못해</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/02/FWT5PD42TZED7JTIXYCIECCFRE</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/09/SQLLSAZD35ENRIL67EOLKI4DFU</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A031-01</t>
+          <t>A020-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A031</t>
+          <t>A020</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>부동산/주택 (⚠판단불가 후보)</t>
+          <t>정치</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>한국 대도시·소도시 집값 격차 3배 'OECD 최대'</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>OECD가 집계한 18국 중 한국에서만 인구 150만명 이상인 대도시의 평균 집값이 10만명 미만 소도시의 3배 이상으로 나왔다.</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>배 이상</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>조사 시점(OECD 보고서 기준)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>18개국 중 최대 격차</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Claude(수동 추출) + 사람 교정 필요</t>
-        </is>
-      </c>
+          <t>김문수 "반명 빅텐트로 대선 이길 것… 한덕수도 함께 해달라" [입장문]</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/21/IXS5JNAIDBA5PDDU3A5TSB3TKM</t>
+          <t>https://www.chosun.com/politics/election2025/2025/05/10/443265BUZ5FUBLXFAMRGRS4NUQ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A032-01</t>
+          <t>A021-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A032</t>
+          <t>A021</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>소비자물가(전체)</t>
+          <t>수출·무역</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>물가 상승률 두 달 연속 2%대...치솟은 기름값, 물가 끌어 올려</t>
+          <t>6월 1~20일 수출 8.3% 증가... 반도체 21.8%↑ 車 9.2%↑</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6일 통계청이 발표한 ‘2월 소비자물가 동향’에 따르면, 지난달 소비자물가지수는 116.08로 전년 동월 대비 2% 상승했다. </t>
+          <t>관세청에 따르면 지난 1~20일 수출액은 386억7200만달러로 전년 동기 대비 8.3% 증가했다.</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1998,12 +1634,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2025년 2월</t>
+          <t>2025-06-01~06-20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2024년 2월 대비</t>
+          <t>2024년 동기 대비</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2013,38 +1649,38 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/06/IXLFBAQ5RFD7HKWH6T3LQXPQWA</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/23/VRSULF3KLRDCXJYUXRMNW45AIY</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A032-02</t>
+          <t>A021-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A032</t>
+          <t>A021</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>소비자물가(석유류)</t>
+          <t>수출·무역</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>물가 상승률 두 달 연속 2%대...치솟은 기름값, 물가 끌어 올려</t>
+          <t>6월 1~20일 수출 8.3% 증가... 반도체 21.8%↑ 車 9.2%↑</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>지난달 석유류 가격은 전년 동월 대비 6.3% 올라, 1월(7.3%)에 이어 두 달 연속으로 5% 이상의 상승폭을 보였다.</t>
+          <t>반도체와 승용차 등 주력 수출 품목이 각각 21.8%, 9.2% 늘어난 영향이 컸다.</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6.3</v>
+        <v>21.8</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2053,12 +1689,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2025년 2월</t>
+          <t>2025-06-01~06-20</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2024년 2월 대비</t>
+          <t>2024년 동기 대비</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2068,38 +1704,38 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/06/IXLFBAQ5RFD7HKWH6T3LQXPQWA</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/23/VRSULF3KLRDCXJYUXRMNW45AIY</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A032-03</t>
+          <t>A021-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A032</t>
+          <t>A021</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>소비자물가(생활물가)</t>
+          <t>수출·무역</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>물가 상승률 두 달 연속 2%대...치솟은 기름값, 물가 끌어 올려</t>
+          <t>6월 1~20일 수출 8.3% 증가... 반도체 21.8%↑ 車 9.2%↑</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">기름값 부담이 반영된 생활물가지수는 지난달 2.6% 오르며 지난해 7월(3%) 이후 7개월 만에 최대 상승폭을 보였다. </t>
+          <t>반도체와 승용차 등 주력 수출 품목이 각각 21.8%, 9.2% 늘어난 영향이 컸다.</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2108,12 +1744,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2025년 2월</t>
+          <t>2025-06-01~06-20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2024년 2월 대비</t>
+          <t>2024년 동기 대비</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2123,42 +1759,42 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/06/IXLFBAQ5RFD7HKWH6T3LQXPQWA/</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/23/VRSULF3KLRDCXJYUXRMNW45AIY</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A033-01</t>
+          <t>A022-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A033</t>
+          <t>A022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>수출·무역(연간 총수출)</t>
+          <t>소매판매</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>반도체 덕에… 지난해 수출 6838억달러 역대 최대</t>
+          <t>금리 0.25%p 내린 한은... 관세 폭탄·내수 부진에 경기 살리기 선택</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">작년 한 해 전체 수출액이 6838억달러(약 1006조원)로 2023년에 비해 8.2% 증가했다고 산업통상자원부와 관세청이 1일 밝혔다. </t>
+          <t>통계청 발표에 따르면 작년 전국 17개 모든 시도에서 소매 판매가 감소한 것으로 나타났다. 전국적으로는 2.2% 감소했고</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6838</v>
+        <v>2.2</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>억달러</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2178,52 +1814,52 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/02/6MYGM52QIVHUJBIZYYFBUW5IQM</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/25/2RBIFVNKT5ELXID4FUQCFM63G4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A033-02</t>
+          <t>A022-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A033</t>
+          <t>A022</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>수출·무역(무역수지)</t>
+          <t>고용(건설업)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>반도체 덕에… 지난해 수출 6838억달러 역대 최대</t>
+          <t>금리 0.25%p 내린 한은... 관세 폭탄·내수 부진에 경기 살리기 선택</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>작년 한국의 수입액은 전년보다 1.6% 감소한 6320억달러로, 518억달러의 무역 흑자를 기록했다.</t>
+          <t>지난달 건설업 취업자 수는 192만 1000명으로, 코로나 팬데믹 시기였던 2021년 이후 처음으로 200만명 아래로 내려갔다</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>518</v>
+        <v>1921000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>억달러</t>
+          <t>명</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2024년(연간)</t>
+          <t>2025년 1월</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2023년 대비</t>
+          <t>2021년 이후 최초(200만명 하회)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2233,52 +1869,52 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/02/6MYGM52QIVHUJBIZYYFBUW5IQM</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/25/2RBIFVNKT5ELXID4FUQCFM63G4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A033-03</t>
+          <t>A022-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A033</t>
+          <t>A022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>수출·무역(12월 수출)</t>
+          <t>수출·무역</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>반도체 덕에… 지난해 수출 6838억달러 역대 최대</t>
+          <t>금리 0.25%p 내린 한은... 관세 폭탄·내수 부진에 경기 살리기 선택</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>작년 12월 수출은 613억8000만달러로 1년 전 대비 6.6% 늘어 한 달 전(1.4%)에 비해 오름폭을 키웠다.</t>
+          <t xml:space="preserve"> 관세청에 따르면 이달 1~20일 수출액은 353억달러로 전년보다 16% 늘었지만,</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>613.8</v>
+        <v>16</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>억달러</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2024년 12월</t>
+          <t>2025-02-01~02-20</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2023년 12월 대비</t>
+          <t>2024년 동기 대비</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2288,38 +1924,38 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/02/6MYGM52QIVHUJBIZYYFBUW5IQM</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/25/2RBIFVNKT5ELXID4FUQCFM63G4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A033-04</t>
+          <t>A023-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A033</t>
+          <t>A023</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>수출·무역(반도체 12월)</t>
+          <t>소비자물가</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>반도체 덕에… 지난해 수출 6838억달러 역대 최대</t>
+          <t>물가상승률 석 달째 2%대...업체들 줄인상에 가공식품·외식 가격 ↑</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>수출 증가율은 작년 8월(10.9%)부터 11월까지 꺾이다가 지난달 들어 반도체 수출이 31.5% 불어나며 오름세로 돌아섰다.</t>
+          <t>2일 통계청이 발표한 ‘3월 소비자물가 동향’에 따르면, 지난달 소비자물가 지수는 116.29로 전년 동월 대비 2.1% 상승했다.</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>31.5</v>
+        <v>2.1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2328,12 +1964,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2024년 12월</t>
+          <t>2025년 3월</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2023년 12월 대비</t>
+          <t>2024년 3월 대비</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2343,52 +1979,52 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/02/6MYGM52QIVHUJBIZYYFBUW5IQM</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/04/02/EZEOHOZC5NBBHKNEXYWAAYWO24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A034-01</t>
+          <t>A023-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A034</t>
+          <t>A023</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>온라인쇼핑(전체 거래액)</t>
+          <t>소비자물가(가공식품)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>내수 부진에 온라인 쇼핑마저 주춤… 가방 거래는 1년4개월 연속↓</t>
+          <t>물가상승률 석 달째 2%대...업체들 줄인상에 가공식품·외식 가격 ↑</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>통계청은 2일 발표한 ‘4월 온라인 쇼핑 동향’에서 지난 4월 온라인 쇼핑 거래액이 21조6858억원으로 전년 동월 대비 2.5% 늘었다고 밝혔다.</t>
+          <t>지난달 가공식품 물가는 전년 동월 대비 3.6% 올랐는데, 지난해 1월(3.2%) 이후 14개월 만에 최대 증가폭이다.</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>21685800000000</v>
+        <v>3.6</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>원</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2025년 4월</t>
+          <t>2025년 3월</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2024년 4월 대비</t>
+          <t>2024년 3월 대비</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2398,38 +2034,38 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/02/NP7AYM35FBDMHIX6A74PKMOFHQ</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/04/02/EZEOHOZC5NBBHKNEXYWAAYWO24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A034-02</t>
+          <t>A023-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A034</t>
+          <t>A023</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>온라인쇼핑(가방)</t>
+          <t>소비자물가(외식)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>내수 부진에 온라인 쇼핑마저 주춤… 가방 거래는 1년4개월 연속↓</t>
+          <t>물가상승률 석 달째 2%대...업체들 줄인상에 가공식품·외식 가격 ↑</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>작년 4월까지만 해도 증가율이 11.5%에 달했는데, 작년 5월(8.7%)부터 지난 4월까지 12개월 연속으로 한 자릿수 성장세를 기록했다.</t>
+          <t>외식 물가는 지난 2월(3%)에 이어 지난달에도 3% 상승했는데,</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-11.3</v>
+        <v>3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2438,12 +2074,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2025년 4월</t>
+          <t>2025년 3월</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2024년 4월 대비</t>
+          <t>2024년 3월 대비</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2453,52 +2089,52 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/02/NP7AYM35FBDMHIX6A74PKMOFHQ</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/04/02/EZEOHOZC5NBBHKNEXYWAAYWO24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A034-03</t>
+          <t>A024-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A034</t>
+          <t>A024</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>온라인쇼핑(이쿠폰)</t>
+          <t>인구동향(출생)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>내수 부진에 온라인 쇼핑마저 주춤… 가방 거래는 1년4개월 연속↓</t>
+          <t>작년 11월 출생아 14.6% 증가...2010년 이후 최대폭</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>이(e)쿠폰 서비스 거래액도 지난해 ‘티메프 사태’ 여파로 인해 1년 전 대비 49.1%나 줄었다.</t>
+          <t xml:space="preserve">22일 통계청이 22일 발표한 ‘2024년 11월 인구동향’에 따르면, 작년 11월 출생아 수는 1년 전에 비해 14.6% 늘어난 2만95명으로 집계됐다. </t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-49.1</v>
+        <v>20095</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>명</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2025년 4월</t>
+          <t>2024년 11월</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2024년 4월 대비</t>
+          <t>2023년 11월 대비</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2508,52 +2144,52 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/02/NP7AYM35FBDMHIX6A74PKMOFHQ</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/01/22/HAHTAVPQ75BJXM4GWC4SNRKAZA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A035-01</t>
+          <t>A024-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A035</t>
+          <t>A024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>고용(산업별 비중)</t>
+          <t>인구동향(누계 출생)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>지난달 보건·복지 산업 종사자 비율, 사상 첫 10% 넘어서</t>
+          <t>작년 11월 출생아 14.6% 증가...2010년 이후 최대폭</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17일 통계청은 지난달 보건·사회복지 서비스업 종사자가 281만2000명으로 전체 취업자(2787만8000명)의 10.1%를 차지했다고 밝혔다.</t>
+          <t>작년 1월부터 11월까지 출생아 수 22만94명으로 전년에 비해 3% 늘어났다.</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10.1</v>
+        <v>220094</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>명</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2025년 1월</t>
+          <t>2024년 1~11월 누계</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2024년 1월(9.7%) 대비</t>
+          <t>2023년 1~11월 대비</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2563,52 +2199,52 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/18/Y6DKXUY4YJAXDAFM64QYC5MPFU</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/01/22/HAHTAVPQ75BJXM4GWC4SNRKAZA</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A035-02</t>
+          <t>A024-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A035</t>
+          <t>A024</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>고용(연간 종사자 증가)</t>
+          <t>인구동향(혼인)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>지난달 보건·복지 산업 종사자 비율, 사상 첫 10% 넘어서</t>
+          <t>작년 11월 출생아 14.6% 증가...2010년 이후 최대폭</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>간병인, 요양보호사 등이 필요한 이들이 늘며, 2014년 170만9000명이었던 보건·복지 종사자는 지난해 294만1000명으로 10년 만에 120만명 불어났다.</t>
+          <t>향후 혼인 추이가 현재의 출생 증가세 유지를 결정하는 주요 변수로 지목되는 가운데, 작년 11월 혼인 건수는 1만8581건으로 1년 전 대비 11.3% 늘었다.</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2941000</v>
+        <v>18581</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>명</t>
+          <t>건</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2024년(연간)</t>
+          <t>2024년 11월</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2014년(1,709,000명) 대비</t>
+          <t>2023년 11월 대비</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2618,42 +2254,42 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/18/Y6DKXUY4YJAXDAFM64QYC5MPFU</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/01/22/HAHTAVPQ75BJXM4GWC4SNRKAZA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A035-03</t>
+          <t>A025-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A035</t>
+          <t>A025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>고용(제조업 비중 하락)</t>
+          <t>인구동향(연간 혼인)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>지난달 보건·복지 산업 종사자 비율, 사상 첫 10% 넘어서</t>
+          <t>작년 혼인 건수 15% 늘어...증가율 1970년 집계 이래 최고</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 제조업 종사자 비율은 2014년 17%에서 지난해 15.6%로 하락한 반면,</t>
+          <t xml:space="preserve">통계청이 26일 발표한 ‘2024년 12월 인구동향’에 따르면, 작년 한해 혼인 건수는 22만2422건으로 전년 대비 14.9% 늘었다. </t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>15.6</v>
+        <v>222422</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>건</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2663,7 +2299,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2014년(17%) 대비</t>
+          <t>2023년 대비</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2673,52 +2309,52 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/18/Y6DKXUY4YJAXDAFM64QYC5MPFU</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/26/GSSMZGGYMBGKXLHSR4WOOWUCQ4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A036-01</t>
+          <t>A025-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A036</t>
+          <t>A025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>부동산/주택(전국 시가총액)</t>
+          <t>인구동향(12월 혼인)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>전국 주택 시총 6839조… 68%가 수도권에</t>
+          <t>작년 혼인 건수 15% 늘어...증가율 1970년 집계 이래 최고</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2023년 말 전국 주택 시가총액은 6839조원으로 집계됐다. </t>
+          <t>작년 12월 혼인 건수는 2만2519건에 달해 전년 동월 대비 28.1% 늘었다.</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6839000000000000</v>
+        <v>22519</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>원</t>
+          <t>건</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2023년 말</t>
+          <t>2024년 12월</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023년 12월 대비</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2728,52 +2364,52 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/27/7CL52K5RZFDOBO7FGPJZSJ75T4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/26/GSSMZGGYMBGKXLHSR4WOOWUCQ4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A036-02</t>
+          <t>A025-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A036</t>
+          <t>A025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>부동산/주택(수도권 비중)</t>
+          <t>인구동향(이혼)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>전국 주택 시총 6839조… 68%가 수도권에</t>
+          <t>작년 혼인 건수 15% 늘어...증가율 1970년 집계 이래 최고</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 이어 경기(1986조원), 부산(389조원), 인천(321조원) 순이었다. 전국에서 서울·경기·인천 등 수도권이 차지하는 비율은 67.7%에 달했다.</t>
+          <t xml:space="preserve">작년 이혼 건수는 9만1155건으로 전년(9만1155건) 대비 1.3% 줄었다. </t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>67.7</v>
+        <v>91155</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>건</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2023년 말</t>
+          <t>2024년(연간)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023년 대비 (※원문 전년치 표기 오타 확인 필요)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2783,54 +2419,52 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/27/7CL52K5RZFDOBO7FGPJZSJ75T4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/26/GSSMZGGYMBGKXLHSR4WOOWUCQ4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A036-03</t>
+          <t>A026-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A036</t>
+          <t>A026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>부동산/주택(유형별 비중)</t>
+          <t>가계동향(전체 소득)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>전국 주택 시총 6839조… 68%가 수도권에</t>
+          <t>1분기 가구당 月 소득 1년 새 4.5% 늘었지만 저소득층은 1.5% 줄어</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>주택 시가총액의 대부분은 아파트로, 전국 기준 아파트 비율은 76.3%로 나타났다. 이어 단독주택(15.5%), 연립·다세대주택(8.2%) 등이 뒤를 이었다.</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>76.3 / 15.5 / 8.2</t>
-        </is>
+          <t>29일 통계청은 ’2025년 1분기 가계동향 조사 결과’에서, 올해 1분기 가구당 월평균 소득이 535만1000원으로 지난해 같은 기간 대비 4.5% 증가했다고 밝혔다.</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>5351000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>원</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2023년 말</t>
+          <t>2025년 1분기</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024년 1분기 대비</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2840,52 +2474,52 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/27/7CL52K5RZFDOBO7FGPJZSJ75T4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/30/PVQ5FXMBSFCETC4MIINOSK535M</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A037-01</t>
+          <t>A026-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A037</t>
+          <t>A026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>기업활동조사(AI 도입률)</t>
+          <t>가계동향(저소득층 소득)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>대한상의 "AI 도입이 기업 매출 4%, 부가가치 7% 높였다"</t>
+          <t>1분기 가구당 月 소득 1년 새 4.5% 늘었지만 저소득층은 1.5% 줄어</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>현재 국내 기업 AI 도입률은 6.4%(2023년 기준)다.</t>
+          <t>소득 하위 20%(1분위) 가구의 월평균 소득은 114만원으로 1년 전보다 1.5% 줄었다.</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6.4</v>
+        <v>1140000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>원</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2023년</t>
+          <t>2025년 1분기</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2018년(2.8%) 대비</t>
+          <t>2024년 1분기 대비</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2895,52 +2529,52 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/industry-company/2025/06/08/JQLCGNZQWNAYRDLXDNDOJDHC4I</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/30/PVQ5FXMBSFCETC4MIINOSK535M</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A037-02</t>
+          <t>A026-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A037</t>
+          <t>A026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>기업활동조사(산업별 도입률)</t>
+          <t>가계동향(소득분배지표)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>대한상의 "AI 도입이 기업 매출 4%, 부가가치 7% 높였다"</t>
+          <t>1분기 가구당 月 소득 1년 새 4.5% 늘었지만 저소득층은 1.5% 줄어</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (AI도입률) 산업별로는 정보통신업이 26%로 가장 높았지만, 제조업은 4%에 그쳐 산업 간 디지털 격차가 큰 상황이다.</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="n">
-        <v>46138</v>
+          <t xml:space="preserve"> 이에 가구원 수가 같다고 가정해 상위 20%의 소득이 하위 20%의 몇 배인지를 보여주는 지표인 균등화 처분가능소득 5분위 배율은 1분기 6.32배로 전년 같은 기간의 5.98배보다 올랐다. </t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>6.32</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>배</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2023년</t>
+          <t>2025년 1분기</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>산업 간 비교</t>
+          <t>2024년 1분기(5.98배) 대비</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2950,52 +2584,52 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/industry-company/2025/06/08/JQLCGNZQWNAYRDLXDNDOJDHC4I</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/05/30/PVQ5FXMBSFCETC4MIINOSK535M</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A038-01</t>
+          <t>A027-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A038</t>
+          <t>A027</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>고용(전체 취업자수)</t>
+          <t>소비자물가(전체)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>고용 한파… 청년이라 더 추운 겨울</t>
+          <t>돼지고기·계란 고공행진… 축산물 물가 6% 올라</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>15일 통계청이 발표한 ‘2024년 12월 및 연간 고용 동향’에 따르면, 지난달 취업자 수는 2804만1000명으로 전년 동월 대비 5만2000명 감소했다.</t>
+          <t>4일 통계청은 ‘5월 소비자 물가 동향’에서 지난달 소비자 물가가 전년 동월 대비 1.9% 올랐다고 밝혔다.</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>28041000</v>
+        <v>1.9</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>명</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2024년 12월</t>
+          <t>2025년 5월</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2023년 12월 대비</t>
+          <t>2024년 5월 대비</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3005,38 +2639,38 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/16/IYBVLBS7D5AJ3ENSN7WNDOJX2Y</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/05/7CAZV7VZIVDGVJTCK22YR6RKMI</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A038-02</t>
+          <t>A027-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A038</t>
+          <t>A027</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>고용(청년 실업률)</t>
+          <t>소비자물가(축산물)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>고용 한파… 청년이라 더 추운 겨울</t>
+          <t>돼지고기·계란 고공행진… 축산물 물가 6% 올라</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">청년 실업률은 5.9%로 6%에 육박했다. </t>
+          <t>하지만 지난달 돼지고기(8.4%), 국산 쇠고기(5.3%), 계란(3.8%) 등의 가격이 일제히 오르며, 축산물 가격 상승 폭은 6.2%를 기록했다.</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3045,12 +2679,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2024년 12월</t>
+          <t>2025년 5월</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024년 5월 대비</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3060,38 +2694,38 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/16/IYBVLBS7D5AJ3ENSN7WNDOJX2Y</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/05/7CAZV7VZIVDGVJTCK22YR6RKMI</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A038-03</t>
+          <t>A027-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A038</t>
+          <t>A027</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>고용(전체 고용률)</t>
+          <t>소비자물가(생활물가)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>고용 한파… 청년이라 더 추운 겨울</t>
+          <t>돼지고기·계란 고공행진… 축산물 물가 6% 올라</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>인구 대비 취업자 수 비율을 뜻하는 고용률은 지난달 61.4%로 1년 전(61.7%)에 비해 0.3%포인트 떨어졌다.</t>
+          <t>이에 가격이 변하면 소비자들이 민감하게 반응하는 144품목만 추려서 작성한 생활 물가는 전년 동월 대비 2.3% 오르며, 올 들어 최저 상승 폭을 보였다.</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>61.4</v>
+        <v>2.3</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3100,12 +2734,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2024년 12월</t>
+          <t>2025년 5월</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2023년 12월(61.7%) 대비</t>
+          <t>2024년 5월 대비</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3115,52 +2749,52 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/16/IYBVLBS7D5AJ3ENSN7WNDOJX2Y</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/05/7CAZV7VZIVDGVJTCK22YR6RKMI</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A039-01</t>
+          <t>A028-01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A039</t>
+          <t>A028</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>경제성장(전국 GRDP)</t>
+          <t>사회조사(삶의 만족도)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>지역 내 총생산 증가율 경북·울산, 1·2위 기록</t>
+          <t>한국 국민 삶 만족도 OECD 38국 중 33위</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">26일 통계청은 ’2025년 1분기 실질 지역내총생산‘ 보고서에서 올해 1분기 전국 지역내총생산 증가율이 0.1%로 집계됐다고 밝혔다. </t>
+          <t>24일 통계청은 ‘국민 삶의 질 2024’ 보고서에서 우리나라 국민들의 지난 3년간(2021~2023년) 평균 삶의 만족도 점수가 6.06점을 기록했다고 밝혔다.</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.1</v>
+        <v>6.06</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>점</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2025년 1분기</t>
+          <t xml:space="preserve">	2021~2023년 평균</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>전분기 대비</t>
+          <t>OECD 38개국 순위 비교(33위)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3170,54 +2804,52 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/27/GX3LOU75LRESZFROWV2AS7IDFE</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/25/7PFLVADLU5CBDNFI3Q4SI5DAEU</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A039-02</t>
+          <t>A028-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A039</t>
+          <t>A028</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>경제성장(시도별 GRDP)</t>
+          <t>사회조사(삶의 만족도)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>지역 내 총생산 증가율 경북·울산, 1·2위 기록</t>
+          <t>한국 국민 삶 만족도 OECD 38국 중 33위</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">시도별 증가율을 보면, 경북(1.6%), 울산(1.4%), 서울(1.0%) 순으로 높았다. </t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1.6 / 1.4 / 1.0</t>
-        </is>
+          <t>2023년 우리나라 국민들의 삶의 만족도는 10점 만점에 6.4점으로 전년 대비 0.1점 감소했다.</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>6.4</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>점</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2025년 1분기</t>
+          <t>2023년</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>시도 간 비교</t>
+          <t>2022년 대비</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3227,38 +2859,38 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/27/GX3LOU75LRESZFROWV2AS7IDFE</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/25/7PFLVADLU5CBDNFI3Q4SI5DAEU</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A039-03</t>
+          <t>A029-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A039</t>
+          <t>A029</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>경제성장(건설업 GRDP)</t>
+          <t>교육(고학력자 비율)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>지역 내 총생산 증가율 경북·울산, 1·2위 기록</t>
+          <t>女 대졸 이상 비율, 80년대생부터 男 앞서</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">특히 건설업 불황은 전국적으로 심각한 상태였다. 올해 1분기 건설업 GRDP는 전년 같은 기간 대비 12.4% 감소했다. </t>
+          <t>반면 1980~1984년생부터는 여성의 고학력자 비율이 72.1%로 남성(69.4%)을 2.7%포인트 앞섰다.</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-12.4</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3267,12 +2899,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2025년 1분기</t>
+          <t>1980~1984년생 코호트</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2024년 1분기 대비</t>
+          <t>남성(69.4%) 대비</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3282,52 +2914,52 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/27/GX3LOU75LRESZFROWV2AS7IDFE</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/28/FV56ZTW6QJB45D7N322ZPHFHYU</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A040-01</t>
+          <t>A029-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A040</t>
+          <t>A029</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>고용(청년 쉬었음 인구)</t>
+          <t>교육(고학력자 비율)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>쉬었음' 청년 50만명 넘어서... 청년 고용률 49개월 만에 최대 낙폭</t>
+          <t>女 대졸 이상 비율, 80년대생부터 男 앞서</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12일 통계청은 ‘2월 고용 동향’에서 지난달 15~29세 청년층의 ‘쉬었음’ 인구가 50만4000명으로 전년 같은 달 대비 6만1000명 늘었다고 밝혔다.</t>
+          <t>1990~1994년생 여성의 대학 이상 졸업자 비율은 78.5%로 남성(65.3%)보다 무려 13%포인트 이상 높았다.</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>504000</v>
+        <v>78.5</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>명</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2025년 2월</t>
+          <t>1990~1994년생 코호트</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2024년 2월 대비</t>
+          <t>남성(65.3%) 대비</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3337,38 +2969,38 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/12/RYNZ7HLF3JCOJKSPPE4VJMSTEE</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/28/FV56ZTW6QJB45D7N322ZPHFHYU</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A040-02</t>
+          <t>A030-01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A040</t>
+          <t>A030</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>고용(청년 고용률)</t>
+          <t>경제성장 (⚠판단불가 후보)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>'쉬었음' 청년 50만명 넘어서... 청년 고용률 49개월 만에 최대 낙폭</t>
+          <t>정부 "올해 경제성장률 1.8%"… 한은 전망보다 더 낮췄다</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 지난달 청년층 고용률은 44.3%에 그치며 전년 같은 달 대비 1.7%포인트 감소했다. </t>
+          <t>수출과 건설 경기 부진 여파로 새해 우리나라 경제가 1.8% 성장하는 데 그칠 것이라고 기획재정부가 2일 전망했다.</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>44.3</v>
+        <v>1.8</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3377,12 +3009,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2025년 2월</t>
+          <t>2025년(전망치)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2024년 2월 대비</t>
+          <t>한국은행 전망(1.9%) 대비</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3392,52 +3024,52 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/12/RYNZ7HLF3JCOJKSPPE4VJMSTEE</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/01/02/FWT5PD42TZED7JTIXYCIECCFRE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A040-03</t>
+          <t>A031-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A040</t>
+          <t>A031</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>고용(청년 취업자수)</t>
+          <t>부동산/주택 (⚠판단불가 후보)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>'쉬었음' 청년 50만명 넘어서... 청년 고용률 49개월 만에 최대 낙폭</t>
+          <t>한국 대도시·소도시 집값 격차 3배 'OECD 최대'</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">청년 취업자는 355만7000명으로 1년 새 23만5000명 줄었다. </t>
+          <t>OECD가 집계한 18국 중 한국에서만 인구 150만명 이상인 대도시의 평균 집값이 10만명 미만 소도시의 3배 이상으로 나왔다.</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3557000</v>
+        <v>3</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>명</t>
+          <t>배 이상</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2025년 2월</t>
+          <t>조사 시점(OECD 보고서 기준)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2024년 2월 대비</t>
+          <t>18개국 중 최대 격차</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3447,54 +3079,52 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/12/RYNZ7HLF3JCOJKSPPE4VJMSTEE</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/21/IXS5JNAIDBA5PDDU3A5TSB3TKM</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A041-01</t>
+          <t>A032-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A041</t>
+          <t>A032</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>가계금융복지(생활비)</t>
+          <t>소비자물가(전체)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>죽어야 받는 종신보험, 살아서 연금으로 받는다</t>
+          <t>물가 상승률 두 달 연속 2%대...치솟은 기름값, 물가 끌어 올려</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>통계청이 작년 12월 발표한 ‘2024년 가계금융복지조사 결과’에 따르면 은퇴한 가구의 월 최소 생활비(2인 기준)는 240만원, 적정 생활비는 월 336만원이다.</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2,400,000 / 3,360,000</t>
-        </is>
+          <t xml:space="preserve">6일 통계청이 발표한 ‘2월 소비자물가 동향’에 따르면, 지난달 소비자물가지수는 116.08로 전년 동월 대비 2% 상승했다. </t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>원</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2024년</t>
+          <t>2025년 2월</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024년 2월 대비</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3504,40 +3134,38 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/12/32Q7YGKIPBCYDEMNFI43L3Z3LU</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/06/IXLFBAQ5RFD7HKWH6T3LQXPQWA</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A041-02</t>
+          <t>A032-02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A041</t>
+          <t>A032</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>가계금융복지(생활비 여유도)</t>
+          <t>소비자물가(석유류)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>죽어야 받는 종신보험, 살아서 연금으로 받는다</t>
+          <t>물가 상승률 두 달 연속 2%대...치솟은 기름값, 물가 끌어 올려</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 그런데 생활비에 ‘여유 있다’는 답한 비율은 10.5%에 불과하고, 절반이 넘는 57%는 ‘부족하다’는 답했다.</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>10.5 / 57</t>
-        </is>
+          <t>지난달 석유류 가격은 전년 동월 대비 6.3% 올라, 1월(7.3%)에 이어 두 달 연속으로 5% 이상의 상승폭을 보였다.</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>6.3</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3546,12 +3174,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2024년</t>
+          <t>2025년 2월</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024년 2월 대비</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3561,38 +3189,38 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/12/32Q7YGKIPBCYDEMNFI43L3Z3LU</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/06/IXLFBAQ5RFD7HKWH6T3LQXPQWA</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A042-01</t>
+          <t>A032-03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A042</t>
+          <t>A032</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>소매판매(연간)</t>
+          <t>소비자물가(생활물가)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>끝이 안 보이는 내수 부진… 소매 판매 21년 만에 최대 감소</t>
+          <t>물가 상승률 두 달 연속 2%대...치솟은 기름값, 물가 끌어 올려</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3일 통계청이 발표한 ‘2024년 12월 및 연간 산업활동 동향’에 따르면, 작년 연간 소매판매액은 전년보다 2.2% 감소했다.</t>
+          <t xml:space="preserve">기름값 부담이 반영된 생활물가지수는 지난달 2.6% 오르며 지난해 7월(3%) 이후 7개월 만에 최대 상승폭을 보였다. </t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3601,12 +3229,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2024년(연간)</t>
+          <t>2025년 2월</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2023년 대비</t>
+          <t>2024년 2월 대비</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3616,42 +3244,42 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/04/54YXZORW2RA5FHIRI552AGTUY4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/06/IXLFBAQ5RFD7HKWH6T3LQXPQWA/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A042-02</t>
+          <t>A033-01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A042</t>
+          <t>A033</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>산업생산(연간)</t>
+          <t>수출·무역(연간 총수출)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>끝이 안 보이는 내수 부진… 소매 판매 21년 만에 최대 감소</t>
+          <t>반도체 덕에… 지난해 수출 6838억달러 역대 최대</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>다만 반도체를 중심으로 수출 실적이 회복되면서 작년 산업 생산은 1.7% 늘어 전년(1%)에 비해 증가 폭이 커졌다.</t>
+          <t xml:space="preserve">작년 한 해 전체 수출액이 6838억달러(약 1006조원)로 2023년에 비해 8.2% 증가했다고 산업통상자원부와 관세청이 1일 밝혔다. </t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.7</v>
+        <v>6838</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>억달러</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3661,7 +3289,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2023년(1%) 대비</t>
+          <t>2023년 대비</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3671,42 +3299,42 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/04/54YXZORW2RA5FHIRI552AGTUY4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/01/02/6MYGM52QIVHUJBIZYYFBUW5IQM</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A042-03</t>
+          <t>A033-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A042</t>
+          <t>A033</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>건설기성(연간)</t>
+          <t>수출·무역(무역수지)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>끝이 안 보이는 내수 부진… 소매 판매 21년 만에 최대 감소</t>
+          <t>반도체 덕에… 지난해 수출 6838억달러 역대 최대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>건설 경기가 얼어붙으면서 토목·건축 분야 건설 실적을 뜻하는 ‘건설기성’도 작년 한 해 4.9%나 줄어 2021년(-6.7%) 이후 3년 만에 가장 큰 낙폭을 보였다.</t>
+          <t>작년 한국의 수입액은 전년보다 1.6% 감소한 6320억달러로, 518억달러의 무역 흑자를 기록했다.</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-4.9</v>
+        <v>518</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>억달러</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3716,7 +3344,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2021년(-6.7%) 대비</t>
+          <t>2023년 대비</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3726,918 +3354,920 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/04/54YXZORW2RA5FHIRI552AGTUY4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/01/02/6MYGM52QIVHUJBIZYYFBUW5IQM</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A043-01</t>
+          <t>A033-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A043</t>
+          <t>A033</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>물가</t>
+          <t>수출·무역(12월 수출)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>물가 상승률 4개월 째 2%대...근원물가 13개월 만 가장 많이 올라</t>
+          <t>반도체 덕에… 지난해 수출 6838억달러 역대 최대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2일 통계청이 발표한 '4월 소비자물가 동향'에 따르면, 지난달 소비자물가 지수는 116.38로 전년 동월 대비 2.1% 올랐다.</t>
+          <t>작년 12월 수출은 613억8000만달러로 1년 전 대비 6.6% 늘어 한 달 전(1.4%)에 비해 오름폭을 키웠다.</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>116.38</v>
+        <v>613.8</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>지수(2020=100)</t>
+          <t>억달러</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024년 12월</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2024년 4월</t>
+          <t>2023년 12월 대비</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/05/02/SSY7QNJ4L5DGFGPEGDWAOOA7HE</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/01/02/6MYGM52QIVHUJBIZYYFBUW5IQM</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A044-01</t>
+          <t>A033-04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A044</t>
+          <t>A033</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>가계부채</t>
+          <t>수출·무역(반도체 12월)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>작년 가계빚 41조 늘어난 1927조원...역대 최고치</t>
+          <t>반도체 덕에… 지난해 수출 6838억달러 역대 최대</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>18일 한국은행은 작년 말 우리나라 가계신용 잔액이 1927조3000억원으로 전년보다 41조8000억원(2.2%) 늘었다고 밝혔다.</t>
+          <t>수출 증가율은 작년 8월(10.9%)부터 11월까지 꺾이다가 지난달 들어 반도체 수출이 31.5% 불어나며 오름세로 돌아섰다.</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1927.3</v>
+        <v>31.5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>조원</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2024-Q4</t>
+          <t>2024년 12월</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2023년 말</t>
+          <t>2023년 12월 대비</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/18/R2YC75IKMRBWVONVGQIRQ7TKYI</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/01/02/6MYGM52QIVHUJBIZYYFBUW5IQM</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A045-01</t>
+          <t>A034-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A045</t>
+          <t>A034</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>외환</t>
+          <t>온라인쇼핑(전체 거래액)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>환율 방어 쓰였지만...지난달 외환보유액 2억 달러↑</t>
+          <t>내수 부진에 온라인 쇼핑마저 주춤… 가방 거래는 1년4개월 연속↓</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>한국은행이 6일 발표한 외환보유액 통계에 따르면 작년 12월말 기준 우리나라 외환보유액은 4156억달러(약 711조7632억원)으로 집계됐다.</t>
+          <t>통계청은 2일 발표한 ‘4월 온라인 쇼핑 동향’에서 지난 4월 온라인 쇼핑 거래액이 21조6858억원으로 전년 동월 대비 2.5% 늘었다고 밝혔다.</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>4156</v>
+        <v>21685800000000</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>억달러</t>
+          <t>원</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025년 4월</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2024년 11월말</t>
+          <t>2024년 4월 대비</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/06/YNGVH2UQHNG7HBDXBGVNC3SXYU</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/02/NP7AYM35FBDMHIX6A74PKMOFHQ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A046-01</t>
+          <t>A034-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A046</t>
+          <t>A034</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>자영업·폐업</t>
+          <t>온라인쇼핑(가방)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>폐업자 작년 100만명 처음 넘어서... “극심한 내수 경기 부진”</t>
+          <t>내수 부진에 온라인 쇼핑마저 주춤… 가방 거래는 1년4개월 연속↓</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6일 국세청 국세 통계에 따르면, 지난해 개인, 법인을 합쳐 폐업 신고를 한 사업자는 100만8282명이었다.</t>
+          <t>작년 4월까지만 해도 증가율이 11.5%에 달했는데, 작년 5월(8.7%)부터 지난 4월까지 12개월 연속으로 한 자릿수 성장세를 기록했다.</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1008282</v>
+        <v>-11.3</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>명</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025년 4월</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2023년</t>
+          <t>2024년 4월 대비</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/07/06/MYX4T7Y46NCY5HUQJZU7C6XRAM</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/02/NP7AYM35FBDMHIX6A74PKMOFHQ</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A047-01</t>
+          <t>A034-03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A047</t>
+          <t>A034</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>부동산·국민순자산</t>
+          <t>온라인쇼핑(이쿠폰)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>우리나라 가구당 순자산 약 6억원, 주택이 절반 이상 차지...전체 국민순자산은 2경4105조원으로 집계</t>
+          <t>내수 부진에 온라인 쇼핑마저 주춤… 가방 거래는 1년4개월 연속↓</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>이 중 우리나라 전체 주택 시가총액은 7158조원으로 추정된다.</t>
+          <t>이(e)쿠폰 서비스 거래액도 지난해 ‘티메프 사태’ 여파로 인해 1년 전 대비 49.1%나 줄었다.</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>7158</v>
+        <v>-49.1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>조원</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025년 4월</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>전년</t>
+          <t>2024년 4월 대비</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/07/17/NK56CBTS5BH4THD2J2OCG5PQZI</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/02/NP7AYM35FBDMHIX6A74PKMOFHQ</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A048-01</t>
+          <t>A035-01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A048</t>
+          <t>A035</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>소비심리</t>
+          <t>고용(산업별 비중)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>계엄 이후 얼어붙은 내수... 덜 먹고 덜 놀러갔다</t>
+          <t>지난달 보건·복지 산업 종사자 비율, 사상 첫 10% 넘어서</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>소비 심리를 나타내는 소비자심리지수(CCSI)는 12월 88.4로 전월보다 12.3포인트 급락했다.</t>
+          <t>17일 통계청은 지난달 보건·사회복지 서비스업 종사자가 281만2000명으로 전체 취업자(2787만8000명)의 10.1%를 차지했다고 밝혔다.</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>88.40000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>지수</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025년 1월</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2024년 11월</t>
+          <t>2024년 1월(9.7%) 대비</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/06/UNEVPXHOQFFWRGCMGJ72EICGC4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/18/Y6DKXUY4YJAXDAFM64QYC5MPFU</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A049-01</t>
+          <t>A035-02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A049</t>
+          <t>A035</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>경기동향</t>
+          <t>고용(연간 종사자 증가)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5월 생산·투자 2달째 동반 감소... 소비도 3달째 반등 못해</t>
+          <t>지난달 보건·복지 산업 종사자 비율, 사상 첫 10% 넘어서</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>현재 경기의 호황·불황 여부를 보여주는 동행종합지수 순환변동치는 지난달 98.5로 전달 대비 0.4포인트 하락했다.</t>
+          <t>간병인, 요양보호사 등이 필요한 이들이 늘며, 2014년 170만9000명이었던 보건·복지 종사자는 지난해 294만1000명으로 10년 만에 120만명 불어났다.</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>98.5</v>
+        <v>2941000</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>지수</t>
+          <t>명</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024년(연간)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2025년 4월</t>
+          <t>2014년(1,709,000명) 대비</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/30/2IZSHTWSWNEJ5FGXOMCGGEDVW4</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/18/Y6DKXUY4YJAXDAFM64QYC5MPFU</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A050-01</t>
+          <t>A035-03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A050</t>
+          <t>A035</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>재정</t>
+          <t>고용(제조업 비중 하락)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>나랏빚 1175조… 역대 최대 규모</t>
+          <t>지난달 보건·복지 산업 종사자 비율, 사상 첫 10% 넘어서</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>지난해 우리나라의 국가 채무가 1175조2000억원으로 역대 최대액을 경신했다.</t>
+          <t xml:space="preserve"> 제조업 종사자 비율은 2014년 17%에서 지난해 15.6%로 하락한 반면,</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1175.2</v>
+        <v>15.6</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>조원</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024년(연간)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>역대 최대치 경신</t>
+          <t>2014년(17%) 대비</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/04/09/4CTQZSRADZHCNFX62KXVIZ2XPM</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/18/Y6DKXUY4YJAXDAFM64QYC5MPFU</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A050-02</t>
+          <t>A036-01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A050</t>
+          <t>A036</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>재정</t>
+          <t>부동산/주택(전국 시가총액)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>나랏빚 1175조… 역대 최대 규모</t>
+          <t>전국 주택 시총 6839조… 68%가 수도권에</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>지난해 총수입에서 총지출을 뺀 통합 재정 수지는 43조5000억원 적자로 GDP 대비 1.7%를 차지했다.</t>
+          <t xml:space="preserve"> 2023년 말 전국 주택 시가총액은 6839조원으로 집계됐다. </t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>-43.5</v>
+        <v>6839000000000000</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>조원(적자)</t>
+          <t>원</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023년 말</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>GDP 대비 1.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/04/09/4CTQZSRADZHCNFX62KXVIZ2XPM</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/27/7CL52K5RZFDOBO7FGPJZSJ75T4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A051-01</t>
+          <t>A036-02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A051</t>
+          <t>A036</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>국민연금</t>
+          <t>부동산/주택(수도권 비중)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>“국민연금 못 받을라”... 수급자 41만명 늘때 가입자 57만명 줄어</t>
+          <t>전국 주택 시총 6839조… 68%가 수도권에</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>9일 국민연금공단의 공표통계에 따르면 작년 10월 말 기준 국민연금 전체 가입자 수는 2181만2216명이다.</t>
+          <t xml:space="preserve"> 이어 경기(1986조원), 부산(389조원), 인천(321조원) 순이었다. 전국에서 서울·경기·인천 등 수도권이 차지하는 비율은 67.7%에 달했다.</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>21812216</v>
+        <v>67.7</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>명</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2023년 말</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2023년 말</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/09/OQKNQDJLTBDB3GZ43E2OZO4HII</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/27/7CL52K5RZFDOBO7FGPJZSJ75T4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A051-02</t>
+          <t>A036-03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A051</t>
+          <t>A036</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>국민연금</t>
+          <t>부동산/주택(유형별 비중)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>“국민연금 못 받을라”... 수급자 41만명 늘때 가입자 57만명 줄어</t>
+          <t>전국 주택 시총 6839조… 68%가 수도권에</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>작년 10월 기준 국민연금 수급자 수는 723만5901명(일시금 수급자 포함)으로, 2023년 말(682만2178명) 대비 41만3723명 증가했다.</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>7235901</v>
+          <t>주택 시가총액의 대부분은 아파트로, 전국 기준 아파트 비율은 76.3%로 나타났다. 이어 단독주택(15.5%), 연립·다세대주택(8.2%) 등이 뒤를 이었다.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>76.3 / 15.5 / 8.2</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>명</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2023년 말</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2023년 말</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/09/OQKNQDJLTBDB3GZ43E2OZO4HII</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/27/7CL52K5RZFDOBO7FGPJZSJ75T4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A053-01</t>
+          <t>A037-01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A053</t>
+          <t>A037</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>수출입물가</t>
+          <t>기업활동조사(AI 도입률)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>고환율 쓰나미...수입물가 전년대비 7% 올라</t>
+          <t>대한상의 "AI 도입이 기업 매출 4%, 부가가치 7% 높였다"</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>한국은행이 14일 발표한 수출입물가지수 및 무역수지 통계에 따르면 작년 12월 원화 기준 수입물가지수는 142.14로 전월대비 2.4% 올랐다.</t>
+          <t>현재 국내 기업 AI 도입률은 6.4%(2023년 기준)다.</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>142.14</v>
+        <v>6.4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>지수(2020=100)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2023년</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2024년 11월</t>
+          <t>2018년(2.8%) 대비</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/15/A7RGQGDZHBAYLEWBZEBFOJULHM</t>
+          <t>https://www.chosun.com/economy/industry-company/2025/06/08/JQLCGNZQWNAYRDLXDNDOJDHC4I</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A053-02</t>
+          <t>A037-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A053</t>
+          <t>A037</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>수출입물가</t>
+          <t>기업활동조사(산업별 도입률)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>고환율 쓰나미...수입물가 전년대비 7% 올라</t>
+          <t>대한상의 "AI 도입이 기업 매출 4%, 부가가치 7% 높였다"</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>수출물가지수는 133.75로 전월대비 2.4%, 전년 대비 10.7% 올랐다.</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>133.75</v>
+          <t xml:space="preserve"> (AI도입률) 산업별로는 정보통신업이 26%로 가장 높았지만, 제조업은 4%에 그쳐 산업 간 디지털 격차가 큰 상황이다.</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>46138</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>지수(2020=100)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2023년</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2024년 11월</t>
+          <t>산업 간 비교</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/15/A7RGQGDZHBAYLEWBZEBFOJULHM</t>
+          <t>https://www.chosun.com/economy/industry-company/2025/06/08/JQLCGNZQWNAYRDLXDNDOJDHC4I</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A054-01</t>
+          <t>A038-01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A054</t>
+          <t>A038</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>기업경기</t>
+          <t>고용(전체 취업자수)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>기업 체감경기 석달 연속 악화…대기업·중소기업 온도차 3년만에 최대로</t>
+          <t>고용 한파… 청년이라 더 추운 겨울</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>23일 한국은행이 발표한 1월 기업경기조사 결과에 따르면 이달 기업심리지수(CBSI)는 비제조업 위주로 악화하며 전달보다 1.4포인트 하락한 85.9를 기록했다.</t>
+          <t>15일 통계청이 발표한 ‘2024년 12월 및 연간 고용 동향’에 따르면, 지난달 취업자 수는 2804만1000명으로 전년 동월 대비 5만2000명 감소했다.</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>85.90000000000001</v>
+        <v>28041000</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>지수(BSI)</t>
+          <t>명</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024년 12월</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2024년 12월</t>
+          <t>2023년 12월 대비</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/23/4FXTMNBTSBFEFICLTIZALFO5ME</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/01/16/IYBVLBS7D5AJ3ENSN7WNDOJX2Y</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A055-01</t>
+          <t>A038-02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A055</t>
+          <t>A038</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>농업·식생활통계</t>
+          <t>고용(청년 실업률)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>한국인의 '밥심' 어디로?…1인당 쌀 소비량 40년 연속 줄었다</t>
+          <t>고용 한파… 청년이라 더 추운 겨울</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>통계청이 23일 발표한 '2024년 양곡소비량조사 결과'에 따르면, 작년 국민 1인당 쌀 소비량은 1년 전 대비 1.1% 감소한 55.8kg을 기록했다.</t>
+          <t xml:space="preserve">청년 실업률은 5.9%로 6%에 육박했다. </t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>55.8</v>
+        <v>5.9</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024년 12월</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2023년</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/23/PF3ATRZKI5GIPG5TH5RNOAPVGI</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/01/16/IYBVLBS7D5AJ3ENSN7WNDOJX2Y</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A056-01</t>
+          <t>A038-03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A056</t>
+          <t>A038</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>인구이동</t>
+          <t>고용(전체 고용률)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>8월 출생아 수, 전년 동월 대비 3.8% ↑… 증가 폭은 주춤</t>
+          <t>고용 한파… 청년이라 더 추운 겨울</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>이날 함께 발표된 '9월 국내 인구 이동 통계'에 따르면 지난달 거주지를 이동한 이동자 수는 49만4000명으로 전년 동월 대비 6.5%(3만명) 증가했다.</t>
+          <t>인구 대비 취업자 수 비율을 뜻하는 고용률은 지난달 61.4%로 1년 전(61.7%)에 비해 0.3%포인트 떨어졌다.</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>494000</v>
+        <v>61.4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>명</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024년 12월</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2024년 9월</t>
+          <t>2023년 12월(61.7%) 대비</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/policy/policy_sub/2025/10/29/VFRFUY4DDZH4TNR3FPDRDKHHII/</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/01/16/IYBVLBS7D5AJ3ENSN7WNDOJX2Y</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A057-01</t>
+          <t>A039-01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A057</t>
+          <t>A039</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>무역</t>
+          <t>경제성장(전국 GRDP)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>수출 '톱10' 기업 비중 40%로 역대 최대...'대기업 쏠림' 심화</t>
+          <t>지역 내 총생산 증가율 경북·울산, 1·2위 기록</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>국가데이터처가 10일 발표한 '2025년 3분기 기업특성별 무역통계'에 따르면, 3분기 수출액 상위 10개 기업의 무역집중도는 40.0%로 지난해 3분기(37.4%)보다 2.6%포인트 상승했다.</t>
+          <t xml:space="preserve">26일 통계청은 ’2025년 1분기 실질 지역내총생산‘ 보고서에서 올해 1분기 전국 지역내총생산 증가율이 0.1%로 집계됐다고 밝혔다. </t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>40</v>
+        <v>0.1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4646,375 +4276,389 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025년 1분기</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2024년 3분기</t>
+          <t>전분기 대비</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, data_set.csv 신규 선별)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/11/10/STP3LFTONFGQLFJKML7SF2LS24/</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/27/GX3LOU75LRESZFROWV2AS7IDFE</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A058-01</t>
+          <t>A039-02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A058</t>
+          <t>A039</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>인구</t>
+          <t>경제성장(시도별 GRDP)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20대 인구, 70대 이상보다 적다… 통계 작성 이래 처음</t>
+          <t>지역 내 총생산 증가율 경북·울산, 1·2위 기록</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>지난해 20대 인구는 630만2000명으로, 전년보다 19만3000명 줄었다.</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>6302000</v>
+          <t xml:space="preserve">시도별 증가율을 보면, 경북(1.6%), 울산(1.4%), 서울(1.0%) 순으로 높았다. </t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1.6 / 1.4 / 1.0</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>명</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2024년</t>
+          <t>2025년 1분기</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2023년 대비</t>
+          <t>시도 간 비교</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/policy/policy_sub/2025/10/12/YBXDEQKJIBBF7IS5Y2PJ2PO2BU/</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/27/GX3LOU75LRESZFROWV2AS7IDFE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A058-02</t>
+          <t>A039-03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A058</t>
+          <t>A039</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>인구</t>
+          <t>경제성장(건설업 GRDP)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>20대 인구, 70대 이상보다 적다… 통계 작성 이래 처음</t>
+          <t>지역 내 총생산 증가율 경북·울산, 1·2위 기록</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>70대 이상 인구(654만3000명)보다 24만1000명 적은 수치다.</t>
+          <t xml:space="preserve">특히 건설업 불황은 전국적으로 심각한 상태였다. 올해 1분기 건설업 GRDP는 전년 같은 기간 대비 12.4% 감소했다. </t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>6543000</v>
+        <v>-12.4</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>명</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2024년</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>2025년 1분기</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2024년 1분기 대비</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/policy/policy_sub/2025/10/12/YBXDEQKJIBBF7IS5Y2PJ2PO2BU/</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/06/27/GX3LOU75LRESZFROWV2AS7IDFE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A059-01</t>
+          <t>A040-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A059</t>
+          <t>A040</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>경제성장률(분기)</t>
+          <t>고용(청년 쉬었음 인구)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>저조한 내수에 계엄, 탄핵, 여객기 사고 여파까지…4분기 성장 0.1%</t>
+          <t>쉬었음' 청년 50만명 넘어서... 청년 고용률 49개월 만에 최대 낙폭</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>작년 4분기(10~12월) 우리나라 경제가 전분기보다 0.1% 성장하는 데 그쳤다.</t>
+          <t>12일 통계청은 ‘2월 고용 동향’에서 지난달 15~29세 청년층의 ‘쉬었음’ 인구가 50만4000명으로 전년 같은 달 대비 6만1000명 늘었다고 밝혔다.</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0.1</v>
+        <v>504000</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>명</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2024년 4분기</t>
+          <t>2025년 2월</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>전분기 대비</t>
+          <t>2024년 2월 대비</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/01/23/X67EMVNMCNF3PIODGNPUZMAQHU</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/12/RYNZ7HLF3JCOJKSPPE4VJMSTEE</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A060-01</t>
+          <t>A040-02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A060</t>
+          <t>A040</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>수출입</t>
+          <t>고용(청년 고용률)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2024년 수출, 6838억달러로 '역대 최대' 경신</t>
+          <t>'쉬었음' 청년 50만명 넘어서... 청년 고용률 49개월 만에 최대 낙폭</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>작년 수출은 6838억달러로 역대 최대치를 경신했다.</t>
+          <t xml:space="preserve"> 지난달 청년층 고용률은 44.3%에 그치며 전년 같은 달 대비 1.7%포인트 감소했다. </t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>683800000000</v>
+        <v>44.3</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>달러</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2024년</t>
+          <t>2025년 2월</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>역대 최대</t>
+          <t>2024년 2월 대비</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/industry-company/2025/01/01/2UPTGREAPRAWRG4XUBRMLONSKY</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/12/RYNZ7HLF3JCOJKSPPE4VJMSTEE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A061-01</t>
+          <t>A040-03</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A061</t>
+          <t>A040</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>고용(청년 취업자수)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[주간증시전망] 관세 리스크는 진정세… 美 물가·中 경제지표 발표 주목</t>
+          <t>'쉬었음' 청년 50만명 넘어서... 청년 고용률 49개월 만에 최대 낙폭</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>지난주(3월 31일~4월 4일) 코스피 지수는 2557.98포인트(p)로 시작했다.</t>
+          <t xml:space="preserve">청년 취업자는 355만7000명으로 1년 새 23만5000명 줄었다. </t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2557.98</v>
+        <v>3557000</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>포인트</t>
+          <t>명</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2025-03(월말)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>2025년 2월</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2024년 2월 대비</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/money/2025/04/06/4NTOH2YJEVXYO2QSGKQJZJEVXE</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/12/RYNZ7HLF3JCOJKSPPE4VJMSTEE</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A062-01</t>
+          <t>A041-01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A062</t>
+          <t>A041</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>국제투자</t>
+          <t>가계금융복지(생활비)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>국내 투자자, 해외 주식·채권 투자 1조달러 첫 돌파</t>
+          <t>죽어야 받는 종신보험, 살아서 연금으로 받는다</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>한국은행은 28일 올해 3월 말 기준 우리나라 대외금융자산 중 증권 투자가 1조118억달러(약 1400조원)를 기록했다고 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>101180000000</v>
+          <t>통계청이 작년 12월 발표한 ‘2024년 가계금융복지조사 결과’에 따르면 은퇴한 가구의 월 최소 생활비(2인 기준)는 240만원, 적정 생활비는 월 336만원이다.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2,400,000 / 3,360,000</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>달러</t>
+          <t>원</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2025년 1분기</t>
+          <t>2024년</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>전분기 대비 176억달러 증가</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/05/29/6M6CLL7Q6JFORJUMOS5SNWHD5M</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/12/32Q7YGKIPBCYDEMNFI43L3Z3LU</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A063-01</t>
+          <t>A041-02</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>A063</t>
+          <t>A041</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>산업생산</t>
+          <t>가계금융복지(생활비 여유도)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>반도체 슈퍼사이클, 9월 생산·투자 끌어올렸다… 기재부는 “새 정부 정책 영향”</t>
+          <t>죽어야 받는 종신보험, 살아서 연금으로 받는다</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>반도체 슈퍼사이클이 9월 산업 전반의 생산과 투자 증가를 이끌었다(9월 전 산업 생산 1.0% 증가).</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>1</v>
+          <t xml:space="preserve"> 그런데 생활비에 ‘여유 있다’는 답한 비율은 10.5%에 불과하고, 절반이 넘는 57%는 ‘부족하다’는 답했다.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>10.5 / 57</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5023,112 +4667,112 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2025년 9월</t>
+          <t>2024년</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>전월 대비</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/policy/policy_sub/2025/10/31/4Y6EBBYW6BFSXKJ5SAD23PF2OI/</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/03/12/32Q7YGKIPBCYDEMNFI43L3Z3LU</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A064-01</t>
+          <t>A042-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>A064</t>
+          <t>A042</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>외국인투자</t>
+          <t>소매판매(연간)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>트럼프 관세 여파로 외국인 직접투자액 1분기 9.2% 줄어</t>
+          <t>끝이 안 보이는 내수 부진… 소매 판매 21년 만에 최대 감소</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>산업통상자원부는 올 1분기 FDI 신고액이 64억1000만달러(약 9조4000억원)를 기록했다고 3일 밝혔다.</t>
+          <t>3일 통계청이 발표한 ‘2024년 12월 및 연간 산업활동 동향’에 따르면, 작년 연간 소매판매액은 전년보다 2.2% 감소했다.</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>6410000000</v>
+        <v>-2.2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>달러</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2025년 1분기</t>
+          <t>2024년(연간)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>작년 같은 기간 대비 9.2% 감소</t>
+          <t>2023년 대비</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/industry-company/2025/04/04/HWJVCRJQ5FDRPI7DW3X5AERARI</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/04/54YXZORW2RA5FHIRI552AGTUY4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A065-01</t>
+          <t>A042-02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>A065</t>
+          <t>A042</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>국제수지</t>
+          <t>산업생산(연간)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>경상수지 역대 둘째로 많은 흑자 낸 까닭은</t>
+          <t>끝이 안 보이는 내수 부진… 소매 판매 21년 만에 최대 감소</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>한국은행은 6일 작년 우리나라의 연간 경상수지 흑자가 990억4000만달러로 집계됐다고 밝혔다.</t>
+          <t>다만 반도체를 중심으로 수출 실적이 회복되면서 작년 산업 생산은 1.7% 늘어 전년(1%)에 비해 증가 폭이 커졌다.</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>99040000000</v>
+        <v>1.7</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>달러</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5138,48 +4782,48 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2015년 이후 두번째로 많은 흑자</t>
+          <t>2023년(1%) 대비</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/02/07/JXWFUVYXYRFO3OXEWCPCGJUSGE</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/04/54YXZORW2RA5FHIRI552AGTUY4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A066-01</t>
+          <t>A042-03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>A066</t>
+          <t>A042</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>설비투자</t>
+          <t>건설기성(연간)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1월 생산 2.7%↓ 소비 0.6%↓ 투자 14.2%↓ '트리플 감소'</t>
+          <t>끝이 안 보이는 내수 부진… 소매 판매 21년 만에 최대 감소</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>설비투자는 전달 대비 14.2% 감소했다.</t>
+          <t>건설 경기가 얼어붙으면서 토목·건축 분야 건설 실적을 뜻하는 ‘건설기성’도 작년 한 해 4.9%나 줄어 2021년(-6.7%) 이후 3년 만에 가장 큰 낙폭을 보였다.</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>-14.2</v>
+        <v>-4.9</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5188,183 +4832,22 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2025년 1월</t>
+          <t>2024년(연간)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>전월 대비</t>
+          <t>2021년(-6.7%) 대비</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
+          <t>Claude(수동 추출) + 사람 교정 필요</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/03/04/FU65MUD47VCAFLZSKULBHJ3HDY</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>A067-01</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>A067</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>생산자물가</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>국제 유가 하락에 4월 생산자물가 전월보다 하락</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>지난달 생산자물가지수가 전월에 비해 0.1% 하락했다고 한국은행이 23일 밝혔다.</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>2025년 4월</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>전월 대비</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/05/23/EMZ6BBQZAND4DKNQF5RMMDSQEM</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>A068-01</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>A068</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>소득이동</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>더 가팔라진 '富의 사다리'… 소득계층 상승 17%뿐</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2023년 소득 분위(1~5분위)가 전년 대비 한 계단 이상 상승한 사람은 소득이 있는 15세 이상 인구의 17.3%에 그쳤다.</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2023년</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/10/28/BEESNX7GT5CP5F3KPXWZI7JORQ/</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>A069-01</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>A069</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>1인당국민소득</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>작년 한국 1인당 국민소득 3만6745달러... 2년 연속 일본 앞질러</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>우리나라 작년 1인당 국민총소득(GNI)이 2년 연속 일본을 앞선 것으로 집계됐다(3만6745달러).</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>36745</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>달러</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2024년</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>일본 대비 2년 연속 상회</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Claude(data_set.csv 수동 추출)</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>https://www.chosun.com/economy/economy_general/2025/06/05/P2N35XU7BJFIDBL32N3K3SYKKA</t>
+          <t>https://www.chosun.com/economy/economy_general/2025/02/04/54YXZORW2RA5FHIRI552AGTUY4</t>
         </is>
       </c>
     </row>
